--- a/bakup/customers/mohammad saleh.xlsx
+++ b/bakup/customers/mohammad saleh.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="235">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -679,6 +679,51 @@
   </si>
   <si>
     <t>1405/06/02</t>
+  </si>
+  <si>
+    <t>1405/06/06</t>
+  </si>
+  <si>
+    <t>ایک اس پروتئین بار</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>دنگ باغ ممد جواد</t>
+  </si>
+  <si>
+    <t>1405/06/16</t>
+  </si>
+  <si>
+    <t>1405/06/21</t>
+  </si>
+  <si>
+    <t>دنگ سس</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>کوصشر گوشی عرشیا</t>
+  </si>
+  <si>
+    <t>شومول</t>
+  </si>
+  <si>
+    <t>1405/07/13</t>
+  </si>
+  <si>
+    <t>1405/07/14</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
   </si>
 </sst>
 </file>
@@ -807,7 +852,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1226,8 +1292,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B218</f>
-        <v>518000</v>
+        <f>B244</f>
+        <v>-9000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4076,88 +4142,128 @@
     <row r="209" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <f t="shared" ref="A209:A215" si="16">A208+B209-C209</f>
-        <v>518000</v>
-      </c>
-      <c r="B209" s="8"/>
+        <v>778000</v>
+      </c>
+      <c r="B209" s="8">
+        <v>260000</v>
+      </c>
       <c r="C209" s="8"/>
-      <c r="D209" s="1"/>
-      <c r="E209" s="1"/>
+      <c r="D209" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="210" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
-      </c>
-      <c r="B210" s="8"/>
+        <v>894000</v>
+      </c>
+      <c r="B210" s="8">
+        <v>116000</v>
+      </c>
       <c r="C210" s="8"/>
-      <c r="D210" s="1"/>
-      <c r="E210" s="1"/>
+      <c r="D210" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="211" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
+        <v>0</v>
       </c>
       <c r="B211" s="8"/>
-      <c r="C211" s="8"/>
-      <c r="D211" s="1"/>
-      <c r="E211" s="1"/>
+      <c r="C211" s="8">
+        <v>894000</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="212" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
-      </c>
-      <c r="B212" s="8"/>
+        <v>155000</v>
+      </c>
+      <c r="B212" s="8">
+        <v>155000</v>
+      </c>
       <c r="C212" s="8"/>
-      <c r="D212" s="1"/>
-      <c r="E212" s="1"/>
+      <c r="D212" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="213" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
-      </c>
-      <c r="B213" s="8"/>
+        <v>355000</v>
+      </c>
+      <c r="B213" s="8">
+        <v>200000</v>
+      </c>
       <c r="C213" s="8"/>
-      <c r="D213" s="1"/>
+      <c r="D213" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="E213" s="1"/>
     </row>
     <row r="214" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
-      </c>
-      <c r="B214" s="8"/>
+        <v>455000</v>
+      </c>
+      <c r="B214" s="8">
+        <v>100000</v>
+      </c>
       <c r="C214" s="8"/>
-      <c r="D214" s="1"/>
-      <c r="E214" s="1"/>
+      <c r="D214" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="215" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <f t="shared" si="16"/>
-        <v>518000</v>
-      </c>
-      <c r="B215" s="8"/>
+        <v>551000</v>
+      </c>
+      <c r="B215" s="8">
+        <v>96000</v>
+      </c>
       <c r="C215" s="8"/>
-      <c r="D215" s="1"/>
-      <c r="E215" s="1"/>
+      <c r="D215" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E215" s="1" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="216" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B216" s="9">
         <f>SUM(B196:B215)+B190</f>
-        <v>11446000</v>
+        <v>12373000</v>
       </c>
       <c r="C216" s="9">
         <f>SUM(C196:C215)+C190</f>
-        <v>10928000</v>
+        <v>11822000</v>
       </c>
     </row>
     <row r="217" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="218" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B218" s="15">
         <f>A215</f>
-        <v>518000</v>
+        <v>551000</v>
       </c>
       <c r="C218" s="17" t="s">
         <v>184</v>
@@ -4165,43 +4271,293 @@
       <c r="D218" s="17"/>
     </row>
     <row r="219" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>10</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C220" s="2"/>
+    </row>
+    <row r="221" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A221" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A222" s="8">
+        <f>B218+B222-C222</f>
+        <v>201000</v>
+      </c>
+      <c r="B222" s="8"/>
+      <c r="C222" s="8">
+        <v>350000</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A223" s="8">
+        <f>A222+B223-C223</f>
+        <v>301000</v>
+      </c>
+      <c r="B223" s="8">
+        <v>100000</v>
+      </c>
+      <c r="C223" s="8"/>
+      <c r="D223" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E223" s="1"/>
+    </row>
+    <row r="224" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A224" s="8">
+        <f t="shared" ref="A224:A231" si="17">A223+B224-C224</f>
+        <v>-99000</v>
+      </c>
+      <c r="B224" s="8"/>
+      <c r="C224" s="8">
+        <v>400000</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A225" s="8">
+        <f t="shared" si="17"/>
+        <v>-59000</v>
+      </c>
+      <c r="B225" s="8">
+        <v>40000</v>
+      </c>
+      <c r="C225" s="8"/>
+      <c r="D225" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A226" s="8">
+        <f t="shared" si="17"/>
+        <v>-9000</v>
+      </c>
+      <c r="B226" s="8">
+        <v>50000</v>
+      </c>
+      <c r="C226" s="8"/>
+      <c r="D226" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A227" s="8">
+        <f t="shared" si="17"/>
+        <v>-9000</v>
+      </c>
+      <c r="B227" s="8"/>
+      <c r="C227" s="8"/>
+      <c r="D227" s="1"/>
+      <c r="E227" s="1"/>
+    </row>
+    <row r="228" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A228" s="8">
+        <f t="shared" si="17"/>
+        <v>-9000</v>
+      </c>
+      <c r="B228" s="8"/>
+      <c r="C228" s="8"/>
+      <c r="D228" s="1"/>
+      <c r="E228" s="1"/>
+    </row>
+    <row r="229" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A229" s="8">
+        <f t="shared" si="17"/>
+        <v>-9000</v>
+      </c>
+      <c r="B229" s="8"/>
+      <c r="C229" s="8"/>
+      <c r="D229" s="1"/>
+      <c r="E229" s="1"/>
+    </row>
+    <row r="230" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A230" s="8">
+        <f t="shared" si="17"/>
+        <v>-9000</v>
+      </c>
+      <c r="B230" s="8"/>
+      <c r="C230" s="8"/>
+      <c r="D230" s="1"/>
+      <c r="E230" s="1"/>
+    </row>
+    <row r="231" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A231" s="8">
+        <f t="shared" si="17"/>
+        <v>-9000</v>
+      </c>
+      <c r="B231" s="8"/>
+      <c r="C231" s="8"/>
+      <c r="D231" s="1"/>
+      <c r="E231" s="1"/>
+    </row>
+    <row r="232" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A232" s="8">
+        <f>A231+B232-C232</f>
+        <v>-9000</v>
+      </c>
+      <c r="B232" s="8"/>
+      <c r="C232" s="8"/>
+      <c r="D232" s="1"/>
+      <c r="E232" s="1"/>
+    </row>
+    <row r="233" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A233" s="8">
+        <f t="shared" ref="A233" si="18">A232+B233-C233</f>
+        <v>-9000</v>
+      </c>
+      <c r="B233" s="8"/>
+      <c r="C233" s="8"/>
+      <c r="D233" s="1"/>
+      <c r="E233" s="1"/>
+    </row>
+    <row r="234" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A234" s="8">
+        <f>A233+B234-C234</f>
+        <v>-9000</v>
+      </c>
+      <c r="B234" s="8"/>
+      <c r="C234" s="8"/>
+      <c r="D234" s="1"/>
+      <c r="E234" s="1"/>
+    </row>
+    <row r="235" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A235" s="8">
+        <f t="shared" ref="A235:A241" si="19">A234+B235-C235</f>
+        <v>-9000</v>
+      </c>
+      <c r="B235" s="8"/>
+      <c r="C235" s="8"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+    </row>
+    <row r="236" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A236" s="8">
+        <f t="shared" si="19"/>
+        <v>-9000</v>
+      </c>
+      <c r="B236" s="8"/>
+      <c r="C236" s="8"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+    </row>
+    <row r="237" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A237" s="8">
+        <f t="shared" si="19"/>
+        <v>-9000</v>
+      </c>
+      <c r="B237" s="8"/>
+      <c r="C237" s="8"/>
+      <c r="D237" s="1"/>
+      <c r="E237" s="1"/>
+    </row>
+    <row r="238" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A238" s="8">
+        <f t="shared" si="19"/>
+        <v>-9000</v>
+      </c>
+      <c r="B238" s="8"/>
+      <c r="C238" s="8"/>
+      <c r="D238" s="1"/>
+      <c r="E238" s="1"/>
+    </row>
+    <row r="239" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A239" s="8">
+        <f t="shared" si="19"/>
+        <v>-9000</v>
+      </c>
+      <c r="B239" s="8"/>
+      <c r="C239" s="8"/>
+      <c r="D239" s="1"/>
+      <c r="E239" s="1"/>
+    </row>
+    <row r="240" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A240" s="8">
+        <f t="shared" si="19"/>
+        <v>-9000</v>
+      </c>
+      <c r="B240" s="8"/>
+      <c r="C240" s="8"/>
+      <c r="D240" s="1"/>
+      <c r="E240" s="1"/>
+    </row>
+    <row r="241" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A241" s="8">
+        <f t="shared" si="19"/>
+        <v>-9000</v>
+      </c>
+      <c r="B241" s="8"/>
+      <c r="C241" s="8"/>
+      <c r="D241" s="1"/>
+      <c r="E241" s="1"/>
+    </row>
+    <row r="242" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B242" s="9">
+        <f>SUM(B222:B241)+B216</f>
+        <v>12563000</v>
+      </c>
+      <c r="C242" s="9">
+        <f>SUM(C222:C241)+C216</f>
+        <v>12572000</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B244" s="15">
+        <f>A241</f>
+        <v>-9000</v>
+      </c>
+      <c r="C244" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D244" s="17"/>
+    </row>
+    <row r="245" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="257" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="258" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="259" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4251,7 +4607,8 @@
     <row r="303" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="304" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C244:D244"/>
     <mergeCell ref="C218:D218"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="C112:D112"/>
@@ -4260,6 +4617,17 @@
     <mergeCell ref="C192:D192"/>
   </mergeCells>
   <conditionalFormatting sqref="B112">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B138">
     <cfRule type="cellIs" dxfId="14" priority="13" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4270,7 +4638,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B138">
+  <conditionalFormatting sqref="B165">
     <cfRule type="cellIs" dxfId="11" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4281,7 +4649,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B165">
+  <conditionalFormatting sqref="B192">
     <cfRule type="cellIs" dxfId="8" priority="7" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4292,7 +4660,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B192">
+  <conditionalFormatting sqref="B218">
     <cfRule type="cellIs" dxfId="5" priority="4" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -4303,7 +4671,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B218">
+  <conditionalFormatting sqref="B244">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
